--- a/output/pdf_financials_xlsx/DST.xlsx
+++ b/output/pdf_financials_xlsx/DST.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.684675</v>
+        <v>3.811294</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.636338</v>
+        <v>6.52886</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.615653</v>
+        <v>2.955183</v>
       </c>
     </row>
     <row r="11">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.033365</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.033365</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -4925,7 +4925,11 @@
           <t>Principal elements of lease payments 7</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>-0.033365</v>
       </c>
@@ -5339,7 +5343,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">

--- a/output/pdf_financials_xlsx/DST.xlsx
+++ b/output/pdf_financials_xlsx/DST.xlsx
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.461373</v>
+        <v>0.481952</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.461381</v>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.172655</v>
+        <v>-3.152076</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-7.21777</v>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.481952</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.461381</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
@@ -4528,7 +4528,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>0.020579</v>
       </c>
@@ -5250,7 +5254,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -5910,7 +5914,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>0.020579</v>
       </c>
